--- a/astro-site/public/dl/guia-chocolateria-obrador/checklist-legal-licencias-y-cacao.xlsx
+++ b/astro-site/public/dl/guia-chocolateria-obrador/checklist-legal-licencias-y-cacao.xlsx
@@ -1567,7 +1567,7 @@
       </c>
       <c r="K7" s="5" t="inlineStr">
         <is>
-          <t>SUPUESTO: la clasificacion urbanistica de un obrador no tiene fuente verificada. Va como PREGUNTA al ayuntamiento, nunca como afirmacion.  [Fuente: supuesto]</t>
+          <t>SUPUESTO: la clasificación urbanística de un obrador no tiene fuente verificada. Va como PREGUNTA al ayuntamiento, nunca como afirmación.  [Fuente: supuesto]</t>
         </is>
       </c>
     </row>
@@ -1584,7 +1584,7 @@
       </c>
       <c r="C8" s="9" t="inlineStr">
         <is>
-          <t>Comprobar que ningun ayuntamiento puede exigirte licencia previa de actividad</t>
+          <t>Comprobar que ningún ayuntamiento puede exigirte licencia previa de actividad</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1618,7 +1618,7 @@
       </c>
       <c r="K8" s="5" t="inlineStr">
         <is>
-          <t>Para las actividades del Anexo de la Ley 12/2012 en establecimientos permanentes de hasta 750 m2 de superficie util de exposicion y venta al publico, NINGUNA administracion puede exigir licencia previa de instalacion, funcionamiento o actividad (`CHN-49`), y el Anexo incluye el grupo 644 completo, con el 644.5 de bombones y caramelos (`CHN-49b`). OJO: la chocolateria de TAZA queda fuera, porque el Anexo no contiene ningun grupo de la agrupacion 67 (`CHN-49c`). Y esta PROHIBIDO decir que tramite pide Madrid o Barcelona.  [Fuente: CHN-49 + CHN-49b]</t>
+          <t>Para las actividades del Anexo de la Ley 12/2012 en establecimientos permanentes de hasta 750 m² de superficie útil de exposición y venta al publico, NINGUNA administración puede exigir licencia previa de instalación, funcionamiento o actividad (`CHN-49`), y el Anexo incluye el grupo 644 completo, con el 644.5 de bombones y caramelos (`CHN-49b`). OJO: la chocolatería de TAZA queda fuera, porque el Anexo no contiene ningún grupo de la agrupación 67 (`CHN-49c`). Y esta PROHIBIDO decir que trámite pide Madrid o Barcelona.  [Fuente: CHN-49 + CHN-49b]</t>
         </is>
       </c>
     </row>
@@ -1669,7 +1669,7 @@
       </c>
       <c r="K9" s="5" t="inlineStr">
         <is>
-          <t>Un obrador de chocolate NO genera aire AE4 (`CHN-46`) y el DB-HS 3 del CTE no regula la ventilacion de un local comercial (`CHN-45`): las reglas de chimenea que circulan son las de las viviendas. Lo que si aplica es el RITE, por la climatizacion.  [Fuente: CHN-45 + CHN-46]</t>
+          <t>Un obrador de chocolate NO genera aire AE4 (`CHN-46`) y el DB-HS 3 del CTE no regula la ventilación de un local comercial (`CHN-45`): las reglas de chimenea que circulan son las de las viviendas. Lo que si aplica es el RITE, por la climatización.  [Fuente: CHN-45 + CHN-46]</t>
         </is>
       </c>
     </row>
@@ -1737,7 +1737,7 @@
       </c>
       <c r="C11" s="9" t="inlineStr">
         <is>
-          <t>Pedir al instalador la potencia frigorifica ofertada y las preguntas de la ficha</t>
+          <t>Pedir al instalador la potencia frigorífica ofertada y las preguntas de la ficha</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1771,7 +1771,7 @@
       </c>
       <c r="K11" s="5" t="inlineStr">
         <is>
-          <t>El libro 1 NO calcula carga termica (D33): compara tu temperatura objetivo, la exterior de agosto de tu ciudad y la potencia que te OFREZCAN, y te da la ficha de preguntas.  [Fuente: supuesto]</t>
+          <t>El libro 1 NO calcula carga térmica (D33): compara tu temperatura objetivo, la exterior de agosto de tu ciudad y la potencia que te OFREZCAN, y te da la ficha de preguntas.  [Fuente: supuesto]</t>
         </is>
       </c>
     </row>
@@ -1815,7 +1815,7 @@
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>F2 · Sociedad, altas fiscales y proyecto tecnico</t>
+          <t>F2 · Sociedad, altas fiscales y proyecto técnico</t>
         </is>
       </c>
       <c r="B14" s="10" t="inlineStr"/>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="C15" s="9" t="inlineStr">
         <is>
-          <t>Constituir la sociedad o darse de alta como autonomo</t>
+          <t>Constituir la sociedad o darse de alta como autónomo</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1874,7 +1874,7 @@
       </c>
       <c r="K15" s="5" t="inlineStr">
         <is>
-          <t>Importa para Verifactu: sociedad, 1-ene-2027; autonomo, 1-jul-2027 (`CHN-75`). NO es 2026.  [Fuente: supuesto]</t>
+          <t>Importa para Verifactu: sociedad, 1-ene-2027; autónomo, 1-jul-2027 (`CHN-75`). NO es 2026.  [Fuente: supuesto]</t>
         </is>
       </c>
     </row>
@@ -1891,7 +1891,7 @@
       </c>
       <c r="C16" s="9" t="inlineStr">
         <is>
-          <t>Alta censal (modelo 036) con los DOS codigos CNAE</t>
+          <t>Alta censal (modelo 036) con los DOS códigos CNAE</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="K16" s="5" t="inlineStr">
         <is>
-          <t>CNAE-2025: 10.82 «Fabricacion de cacao, chocolate y productos de confiteria» y 47.24 «Comercio al por menor de pan, productos de panaderia y confiteria» (`CHN-74`). Y al darte de alta HOY comunicas DOS codigos, no uno: el CNAE-2025 y ademas el CNAE-2009 mientras no entre en vigor la tarifa de primas adaptada (`CHN-74b`).  [Fuente: CHN-74 + CHN-74b]</t>
+          <t>CNAE-2025: 10.82 «Fabricación de cacao, chocolate y productos de confitería» y 47.24 «Comercio al por menor de pan, productos de panadería y confitería» (`CHN-74`). Y al darte de alta HOY comunicas DOS códigos, no uno: el CNAE-2025 y además el CNAE-2009 mientras no entre en vigor la tarifa de primas adaptada (`CHN-74b`).  [Fuente: CHN-74 + CHN-74b]</t>
         </is>
       </c>
     </row>
@@ -1942,7 +1942,7 @@
       </c>
       <c r="C17" s="9" t="inlineStr">
         <is>
-          <t>Alta en el epigrafe 644.5 del IAE, con su nota literal delante</t>
+          <t>Alta en el epígrafe 644.5 del IAE, con su nota literal delante</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1976,7 +1976,7 @@
       </c>
       <c r="K17" s="5" t="inlineStr">
         <is>
-          <t>El 644.5 «Comercio al por menor de bombones y caramelos» FACULTA para fabricar bombones en el propio establecimiento «siempre que su comercializacion se realice en las propias dependencias de venta» (`CHN-72`). Alta si, pago casi nunca: hay exencion por cifra de negocio (`CHN-73`). Y la Regla 4.a.1 dice que una cuota faculta EXCLUSIVAMENTE para su actividad (`CHN-94`): de ahi salen las cinco filas de canal.  [Fuente: CHN-72 + CHN-73 + CHN-94]</t>
+          <t>El 644.5 «Comercio al por menor de bombones y caramelos» FACULTA para fabricar bombones en el propio establecimiento «siempre que su comercialización se realice en las propias dependencias de venta» (`CHN-72`). Alta si, pago casi nunca: hay exención por cifra de negocio (`CHN-73`). Y la Regla 4.a.1 dice que una cuota faculta EXCLUSIVAMENTE para su actividad (`CHN-94`): de ahí salen las cinco filas de canal.  [Fuente: CHN-72 + CHN-73 + CHN-94]</t>
         </is>
       </c>
     </row>
@@ -1993,7 +1993,7 @@
       </c>
       <c r="C18" s="9" t="inlineStr">
         <is>
-          <t>Alta en el regimen correspondiente de la Seguridad Social</t>
+          <t>Alta en el régimen correspondiente de la Seguridad Social</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2044,7 +2044,7 @@
       </c>
       <c r="C19" s="9" t="inlineStr">
         <is>
-          <t>Encargar el proyecto tecnico visado</t>
+          <t>Encargar el proyecto técnico visado</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2076,7 +2076,7 @@
       </c>
       <c r="K19" s="5" t="inlineStr">
         <is>
-          <t>Coste SUPUESTO: `CHN-50` esta en EXCLUIDOS. Es el documento del que cuelga todo lo demas.  [Fuente: supuesto]</t>
+          <t>Coste SUPUESTO: `CHN-50` esta en EXCLUIDOS. Es el documento del que cuelga todo lo demás.  [Fuente: supuesto]</t>
         </is>
       </c>
     </row>
@@ -2169,7 +2169,7 @@
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>F3 · Registro sanitario y comunicacion autonomica</t>
+          <t>F3 · Registro sanitario y comunicación autonómica</t>
         </is>
       </c>
       <c r="B23" s="10" t="inlineStr"/>
@@ -2196,7 +2196,7 @@
       </c>
       <c r="C24" s="9" t="inlineStr">
         <is>
-          <t>Presentar la comunicacion o declaracion responsable al registro autonomico</t>
+          <t>Presentar la comunicación o declaración responsable al registro autonómico</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -2228,7 +2228,7 @@
       </c>
       <c r="K24" s="5" t="inlineStr">
         <is>
-          <t>El minorista esta EXCLUIDO del RGSEAA y se inscribe en el registro de su comunidad mediante comunicacion o declaracion responsable QUE NO HABILITA (`CHN-39`). Y el mismo tramite funciona distinto: en Madrid se presenta simultaneamente al inicio de la actividad y no habilita; en la Comunitat Valenciana es condicion unica y suficiente para iniciar y lleva tasa (`CHN-43`). PROHIBIDO escribir «necesitas el RGSEAA para abrir».  [Fuente: CHN-39 + CHN-43]</t>
+          <t>El minorista esta EXCLUIDO del RGSEAA y se inscribe en el registro de su comunidad mediante comunicación o declaración responsable QUE NO HABILITA (`CHN-39`). Y el mismo trámite funciona distinto: en Madrid se presenta simultaneamente al inicio de la actividad y no habilita; en la Comunitat Valenciana es condición única y suficiente para iniciar y lleva tasa (`CHN-43`). PROHIBIDO escribir «necesitas el RGSEAA para abrir».  [Fuente: CHN-39 + CHN-43]</t>
         </is>
       </c>
     </row>
@@ -2245,7 +2245,7 @@
       </c>
       <c r="C25" s="9" t="inlineStr">
         <is>
-          <t>Resolver el arbol: tener obrador NO te saca de minorista</t>
+          <t>Resolver el árbol: tener obrador NO te saca de minorista</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -2279,7 +2279,7 @@
       </c>
       <c r="K25" s="5" t="inlineStr">
         <is>
-          <t>Tener obrador NO te saca del regimen minorista (`CHN-40b`). La clave y las actividades del RGSEAA solo entran cuando SI toca (`CHN-40`).  [Fuente: CHN-40 + CHN-40b]</t>
+          <t>Tener obrador NO te saca del régimen minorista (`CHN-40b`). La clave y las actividades del RGSEAA solo entran cuando SI toca (`CHN-40`).  [Fuente: CHN-40 + CHN-40b]</t>
         </is>
       </c>
     </row>
@@ -2296,7 +2296,7 @@
       </c>
       <c r="C26" s="9" t="inlineStr">
         <is>
-          <t>Resolver los TRES semaforos del art. 3 si suministras a otros minoristas</t>
+          <t>Resolver los TRES semáforos del art. 3 si suministras a otros minoristas</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="K26" s="5" t="inlineStr">
         <is>
-          <t>PUERTA DE ENTRADA: ¿suministras a otros minoristas de DISTINTA TITULARIDAD? Si la respuesta es no, el art. 3 no te aplica. Si es si, tres semaforos INDEPENDIENTES y ACUMULATIVOS: MARGINAL por la via a) hasta el 25 % del volumen anual O por la b) hasta 500 kg/semana -son dos entradas distintas-; LOCALIZADO, misma zona de salud o hasta 50 km en el caso interautonomico; RESTRINGIDO, que ninguno de tus clientes este inscrito en el RGSEAA. PROHIBIDO «los 500 kg incluyen el mostrador».  [Fuente: CHN-41]</t>
+          <t>PUERTA DE ENTRADA: ¿suministras a otros minoristas de DISTINTA TITULARIDAD? Si la respuesta es no, el art. 3 no te aplica. Si es si, tres semáforos INDEPENDIENTES y ACUMULATIVOS: MARGINAL por la vía a) hasta el 25 % del volumen anual O por la b) hasta 500 kg/semana -son dos entradas distintas-; LOCALIZADO, misma zona de salud o hasta 50 km en el caso interautonomico; RESTRINGIDO, que ninguno de tus clientes este inscrito en el RGSEAA. PROHIBIDO «los 500 kg incluyen el mostrador».  [Fuente: CHN-41]</t>
         </is>
       </c>
     </row>
@@ -2381,7 +2381,7 @@
       </c>
       <c r="K27" s="5" t="inlineStr">
         <is>
-          <t>La lista estatal del obrador en vivienda tiene CINCO letras y la quinta es ABIERTA: «otros alimentos que las autoridades competentes de las comunidades autonomas permitan en sus territorios» (`CHN-44`). Por defecto el chocolate no encaja en la letra b), pero eso es INTERPRETACION DECLARADA (`CHN-44-int`), no nivel A: compruebalo en tu comunidad. La letra b) valenciana anade «confiteria», NO «chocolate» (`CHN-44b`). PROHIBIDO «hacer bombones en casa para vender es ilegal en Espana». Y el tope de 100 kg/semana del art. 13.9 solo se activa si esta casilla esta en «si»: son TRES requisitos, no uno -volumen PROPORCIONAL AL TAMANO DE LAS INSTALACIONES, tope de 100 kg/semana y demostrable documentalmente- y el que de verdad limita es el primero (`PA-29c`, reutilizado de Pasteleria y verificado el 10-09-2026).  [Fuente: CHN-44 + CHN-44-int + CHN-44b]</t>
+          <t>La lista estatal del obrador en vivienda tiene CINCO letras y la quinta es ABIERTA: «otros alimentos que las autoridades competentes de las comunidades autónomas permitan en sus territorios» (`CHN-44`). Por defecto el chocolate no encaja en la letra b), pero eso es INTERPRETACION DECLARADA (`CHN-44-int`), no nivel A: compruebalo en tu comunidad. La letra b) valenciana añade «confitería», NO «chocolate» (`CHN-44b`). PROHIBIDO «hacer bombones en casa para vender es ilegal en Espana». Y el tope de 100 kg/semana del art. 13.9 solo se activa si esta casilla esta en «si»: son TRES requisitos, no uno -volumen PROPORCIONAL AL TAMAÑO DE LAS INSTALACIONES, tope de 100 kg/semana y demostrable documentalmente- y el que de verdad limita es el primero (`PA-29c`, reutilizado de Pastelería y verificado el 10-09-2026).  [Fuente: CHN-44 + CHN-44-int + CHN-44b]</t>
         </is>
       </c>
     </row>
@@ -2452,7 +2452,7 @@
       </c>
       <c r="C31" s="9" t="inlineStr">
         <is>
-          <t>Contratar la obra y la adecuacion</t>
+          <t>Contratar la obra y la adecuación</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2484,7 +2484,7 @@
       </c>
       <c r="K31" s="5" t="inlineStr">
         <is>
-          <t>Coste SUPUESTO. Sin humos, la obra de un obrador de chocolate es mas barata que la de una pasteleria.  [Fuente: supuesto]</t>
+          <t>Coste SUPUESTO. Sin humos, la obra de un obrador de chocolate es mas barata que la de una pastelería.  [Fuente: supuesto]</t>
         </is>
       </c>
     </row>
@@ -2501,7 +2501,7 @@
       </c>
       <c r="C32" s="9" t="inlineStr">
         <is>
-          <t>Contratar la climatizacion con deshumidificacion</t>
+          <t>Contratar la climatización con deshumidificación</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2635,7 +2635,7 @@
       </c>
       <c r="K34" s="5" t="inlineStr">
         <is>
-          <t>Solo si FABRICAS, IMPORTAS o haces ADQUISICION INTRACOMUNITARIA de envases no reutilizables con plastico. La exencion del art. 75.f) (5 kg/mes) cubre solo la importacion y la adquisicion intracomunitaria, y solo los envases del art. 68.1.a): NO la fabricacion, NI los semielaborados, NI los cierres (`CHN-62b`).  [Fuente: CHN-62 + CHN-62b]</t>
+          <t>Solo si FABRICAS, IMPORTAS o haces ADQUISICION INTRACOMUNITARIA de envases no reutilizables con plastico. La exención del art. 75.f) (5 kg/mes) cubre solo la importación y la adquisición intracomunitaria, y solo los envases del art. 68.1.a): NO la fabricación, NI los semielaborados, NI los cierres (`CHN-62b`).  [Fuente: CHN-62 + CHN-62b]</t>
         </is>
       </c>
     </row>
@@ -2652,7 +2652,7 @@
       </c>
       <c r="C35" s="9" t="inlineStr">
         <is>
-          <t>Si hay freidora de gas en la variante de taza, programar la inspeccion</t>
+          <t>Si hay freidora de gas en la variante de taza, programar la inspección</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2686,7 +2686,7 @@
       </c>
       <c r="K35" s="5" t="inlineStr">
         <is>
-          <t>Inspeccion periodica obligatoria de la instalacion receptora CADA CINCO ANOS, que en instalaciones de hasta 70 kW incluye los aparatos y comprueba la ventilacion y el volumen minimo del local (`CHN-48`).  [Fuente: CHN-48]</t>
+          <t>Inspección periódica obligatoria de la instalación receptora CADA CINCO AÑOS, que en instalaciones de hasta 70 kW incluye los aparatos y comprueba la ventilación y el volumen mínimo del local (`CHN-48`).  [Fuente: CHN-48]</t>
         </is>
       </c>
     </row>
@@ -2730,7 +2730,7 @@
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>F5 · APPCC, alergenos y formacion</t>
+          <t>F5 · APPCC, alérgenos y formación</t>
         </is>
       </c>
       <c r="B38" s="10" t="inlineStr"/>
@@ -2791,7 +2791,7 @@
       </c>
       <c r="K39" s="5" t="inlineStr">
         <is>
-          <t>El procedimiento permanente basado en el APPCC puede aplicarse de manera SIMPLIFICADA conforme a la Comunicacion 2020/C 199/01, pero debe contar con una persona responsable de su aplicacion (`CHN-32`). En el APPCC va la vida util que TU declaras (`CHN-30`).  [Fuente: CHN-32]</t>
+          <t>El procedimiento permanente basado en el APPCC puede aplicarse de manera SIMPLIFICADA conforme a la Comunicación 2020/C 199/01, pero debe contar con una persona responsable de su aplicación (`CHN-32`). En el APPCC va la vida útil que TU declaras (`CHN-30`).  [Fuente: CHN-32]</t>
         </is>
       </c>
     </row>
@@ -2808,7 +2808,7 @@
       </c>
       <c r="C40" s="9" t="inlineStr">
         <is>
-          <t>Montar el registro de formacion del personal</t>
+          <t>Montar el registro de formación del personal</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2842,7 +2842,7 @@
       </c>
       <c r="K40" s="5" t="inlineStr">
         <is>
-          <t>EL CARNET DE MANIPULADOR NO EXISTE. La obligacion viva es del empresario: garantizar la formacion de cada persona de acuerdo con su actividad laboral y PODER ACREDITARLA (`CHN-69`). PROHIBIDO escribir «hay que sacarse el carnet de manipulador».  [Fuente: CHN-69]</t>
+          <t>EL CARNET DE MANIPULADOR NO EXISTE. La obligación viva es del empresario: garantizar la formación de cada persona de acuerdo con su actividad laboral y PODER ACREDITARLA (`CHN-69`). PROHIBIDO escribir «hay que sacarse el carnet de manipulador».  [Fuente: CHN-69]</t>
         </is>
       </c>
     </row>
@@ -2859,7 +2859,7 @@
       </c>
       <c r="C41" s="9" t="inlineStr">
         <is>
-          <t>Montar la declaracion de los OCHO alergenos y el protocolo de limpieza</t>
+          <t>Montar la declaración de los OCHO alérgenos y el protocolo de limpieza</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2893,7 +2893,7 @@
       </c>
       <c r="K41" s="5" t="inlineStr">
         <is>
-          <t>OCHO, no cinco (`CHN-34b`). El equipo usado con un alergeno no se reutiliza para otro alimento sin limpiarlo (`CHN-33`). En producto sin envasar los alergenos pueden ir en cartel, pero la fecha no (`CHN-89`).  [Fuente: CHN-34b + CHN-33 + CHN-89]</t>
+          <t>OCHO, no cinco (`CHN-34b`). El equipo usado con un alérgeno no se reutiliza para otro alimento sin limpiarlo (`CHN-33`). En producto sin envasar los alérgenos pueden ir en cartel, pero la fecha no (`CHN-89`).  [Fuente: CHN-34b + CHN-33 + CHN-89]</t>
         </is>
       </c>
     </row>
@@ -2944,7 +2944,7 @@
       </c>
       <c r="K42" s="5" t="inlineStr">
         <is>
-          <t>NO ES EL MISMO REGIMEN (D47). Con etiqueta te obliga lo que tu has escrito en ella (art. 4.2 del RD 1021/2022) mas las doce menciones del art. 9.1 del Rgto. 1169/2011 (`CHN-35`) y el lote, que viene del RD 1808/1991 y NO de ese reglamento (`CHN-36`). A granel, la referencia es TU sistema de autocontrol.  [Fuente: CHN-30 + CHN-35 + CHN-36 + CHN-87]</t>
+          <t>NO ES EL MISMO RÉGIMEN (D47). Con etiqueta te obliga lo que tu has escrito en ella (art. 4.2 del RD 1021/2022) mas las doce menciones del art. 9.1 del Rgto. 1169/2011 (`CHN-35`) y el lote, que viene del RD 1808/1991 y NO de ese reglamento (`CHN-36`). A granel, la referencia es TU sistema de autocontrol.  [Fuente: CHN-30 + CHN-35 + CHN-36 + CHN-87]</t>
         </is>
       </c>
     </row>
@@ -2961,7 +2961,7 @@
       </c>
       <c r="C43" s="9" t="inlineStr">
         <is>
-          <t>Decidir si necesitas analitica de cadmio y con que frecuencia</t>
+          <t>Decidir si necesitas analítica de cadmio y con que frecuencia</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -2995,7 +2995,7 @@
       </c>
       <c r="K43" s="5" t="inlineStr">
         <is>
-          <t>LO QUE ES CHOCOLATE PARA LA DENOMINACION NO LO ES PARA LOS CONTAMINANTES: la nota (14) del Anexo I del Rgto. 2023/915 remite SOLO a los puntos 2, 3 y 4 de la parte A del Anexo I de la Directiva 2000/36/CE -cacao en polvo, chocolate y chocolate con leche- (`CHN-16b`). El BOMBON NO TIENE LIMITE PROPIO DE CADMIO: se le aplica la regla de alimentos compuestos del art. 3 (`CHN-84`). PROHIBIDO «tu bombon tiene un limite de cadmio de X».  [Fuente: CHN-16 + CHN-16b + CHN-84]</t>
+          <t>LO QUE ES CHOCOLATE PARA LA DENOMINACION NO LO ES PARA LOS CONTAMINANTES: la nota (14) del Anexo I del Rgto. 2023/915 remite SOLO a los puntos 2, 3 y 4 de la parte A del Anexo I de la Directiva 2000/36/CE -cacao en polvo, chocolate y chocolate con leche- (`CHN-16b`). El BOMBÓN NO TIENE LIMITE PROPIO DE CADMIO: se le aplica la regla de alimentos compuestos del art. 3 (`CHN-84`). PROHIBIDO «tu bombón tiene un limite de cadmio de X».  [Fuente: CHN-16 + CHN-16b + CHN-84]</t>
         </is>
       </c>
     </row>
@@ -3046,7 +3046,7 @@
       </c>
       <c r="K44" s="5" t="inlineStr">
         <is>
-          <t>El Anexo I incluye la partida 1806 «Chocolate y demas preparaciones alimenticias que contengan cacao», y el reglamento cubre tambien la EXPORTACION (`CHN-20`, `CHN-60`). Fecha general: 30 de diciembre de 2026 (`CHN-21`). El aplazamiento a 30-06-2027 del art. 38.3 es SOLO para «operadores» persona fisica, microempresa o pequena empresa establecidos a 31-12-2024, y el art. 2.15 excluye de esa palabra a los operadores posteriores (`CHN-22`, `CHN-23`). VERIFICADO A 12-09-2026: comprueba el estado del EUDR antes de comprar cacao.  [Fuente: CHN-20 + CHN-21 + CHN-22 + CHN-23 + CHN-24 + CHN-25]</t>
+          <t>El Anexo I incluye la partida 1806 «Chocolate y demás preparaciones alimenticias que contengan cacao», y el reglamento cubre también la EXPORTACION (`CHN-20`, `CHN-60`). Fecha general: 30 de diciembre de 2026 (`CHN-21`). El aplazamiento a 30-06-2027 del art. 38.3 es SOLO para «operadores» persona física, microempresa o pequeña empresa establecidos a 31-12-2024, y el art. 2.15 excluye de esa palabra a los operadores posteriores (`CHN-22`, `CHN-23`). VERIFICADO A 12-09-2026: comprueba el estado del EUDR antes de comprar cacao.  [Fuente: CHN-20 + CHN-21 + CHN-22 + CHN-23 + CHN-24 + CHN-25]</t>
         </is>
       </c>
     </row>
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C48" s="9" t="inlineStr">
         <is>
-          <t>Comprobar que tu comunicacion sanitaria esta presentada antes de vender</t>
+          <t>Comprobar que tu comunicación sanitaria esta presentada antes de vender</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -3202,7 +3202,7 @@
       </c>
       <c r="K49" s="5" t="inlineStr">
         <is>
-          <t>NO EXISTE convenio estatal del chocolate (`CHN-66`). La tabla que trae el producto es la de Madrid y va MARCADA COMO EJEMPLO. Busca el tuyo por AMBITO FUNCIONAL, no por el nombre que te suene: la denominacion oficial del de Madrid es «CONFITERIAS PASTELERIAS Y REPOSTERIA (COMERCIO E INDUSTRIA)» y quien busque «bollerias» no lo encuentra (`CHN-65c`). Cuatro convenios de sector nombran chocolates o bombones (`CHN-93`).  [Fuente: CHN-65 + CHN-65c + CHN-66 + CHN-93]</t>
+          <t>NO EXISTE convenio estatal del chocolate (`CHN-66`). La tabla que trae el producto es la de Madrid y va MARCADA COMO EJEMPLO. Busca el tuyo por ÁMBITO FUNCIONAL, no por el nombre que te suene: la denominación oficial del de Madrid es «CONFITERÍAS PASTELERÍAS Y REPOSTERÍA (COMERCIO E INDUSTRIA)» y quien busque «bollerias» no lo encuentra (`CHN-65c`). Cuatro convenios de sector nombran chocolates o bombones (`CHN-93`).  [Fuente: CHN-65 + CHN-65c + CHN-66 + CHN-93]</t>
         </is>
       </c>
     </row>
@@ -3304,7 +3304,7 @@
       </c>
       <c r="K51" s="5" t="inlineStr">
         <is>
-          <t>Una bomboneria NO esta en la lista del art. 5.1 de la Ley 1/2004 -que nombra «pasteleria y reposteria, pan, platos preparados, prensa, combustibles y carburantes, floristerias y plantas»-: le viene por el art. 5.2, establecimientos de venta de reducida dimension de menos de 300 m2 (`CHN-77`). PROHIBIDO decir que le viene por el 5.1, y prohibido «hay que pedir permiso para abrir en domingo».  [Fuente: CHN-77]</t>
+          <t>Una bombonería NO esta en la lista del art. 5.1 de la Ley 1/2004 -que nombra «pastelería y repostería, pan, platos preparados, prensa, combustibles y carburantes, floristerias y plantas»-: le viene por el art. 5.2, establecimientos de venta de reducida dimensión de menos de 300 m² (`CHN-77`). PROHIBIDO decir que le viene por el 5.1, y prohibido «hay que pedir permiso para abrir en domingo».  [Fuente: CHN-77]</t>
         </is>
       </c>
     </row>
@@ -3372,7 +3372,7 @@
       </c>
       <c r="C53" s="9" t="inlineStr">
         <is>
-          <t>Decidir si publicas precios anteriores, y con la regla de los 30 dias delante</t>
+          <t>Decidir si publicas precios anteriores, y con la regla de los 30 días delante</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -3406,7 +3406,7 @@
       </c>
       <c r="K53" s="5" t="inlineStr">
         <is>
-          <t>Subir en noviembre para «rebajar» en diciembre NO cumple la regla de los 30 dias del art. 20 de la LEY 7/1996 en la redaccion del RDL 24/2021 (`CHN-76`) - que NO es el art. 20 del TRLGDCU. Por eso este producto sale SIN precio tachado.  [Fuente: CHN-76]</t>
+          <t>Subir en noviembre para «rebajar» en diciembre NO cumple la regla de los 30 días del art. 20 de la LEY 7/1996 en la redacción del RDL 24/2021 (`CHN-76`) - que NO es el art. 20 del TRLGDCU. Por eso este producto sale SIN precio tachado.  [Fuente: CHN-76]</t>
         </is>
       </c>
     </row>
@@ -3457,7 +3457,7 @@
       </c>
       <c r="K54" s="5" t="inlineStr">
         <is>
-          <t>El art. 6.6 de la Ley 1/2025 EXCLUYE a las microempresas de las obligaciones de TODOS los apartados anteriores del art. 6 -plan, convenios de donacion, jerarquia- (`CHN-64`). Lo que sigue en pie no es una obligacion tuya: es que cualquier clausula contractual que prohiba donar es nula de pleno derecho. PERO la exclusion NO alcanza al ART. 8 (`CHN-92`), que obliga a las empresas de hosteleria y otros proveedores de servicios alimentarios a facilitar que el consumidor se lleve lo que no ha consumido. PROHIBIDAS las dos frases: «te siguen obligando el 6.2 y el 6.5» y «no te obliga nada de la ley de desperdicio».  [Fuente: CHN-64 + CHN-92]</t>
+          <t>El art. 6.6 de la Ley 1/2025 EXCLUYE a las microempresas de las obligaciones de TODOS los apartados anteriores del art. 6 -plan, convenios de donación, jerarquia- (`CHN-64`). Lo que sigue en pie no es una obligación tuya: es que cualquier clausula contractual que prohíba donar es nula de pleno derecho. PERO la exclusión NO alcanza al ART. 8 (`CHN-92`), que obliga a las empresas de hostelería y otros proveedores de servicios alimentarios a facilitar que el consumidor se lleve lo que no ha consumido. PROHIBIDAS las dos frases: «te siguen obligando el 6.2 y el 6.5» y «no te obliga nada de la ley de desperdicio».  [Fuente: CHN-64 + CHN-92]</t>
         </is>
       </c>
     </row>
@@ -3672,7 +3672,7 @@
     <row r="70" ht="40" customHeight="1">
       <c r="C70" s="8" t="inlineStr">
         <is>
-          <t>¿Vas a inscribirte como artesano alimentario? (comunidad autonoma + enlace)</t>
+          <t>¿Vas a inscribirte como artesano alimentario? (comunidad autónoma + enlace)</t>
         </is>
       </c>
       <c r="D70" s="11" t="inlineStr">
@@ -3682,7 +3682,7 @@
       </c>
       <c r="K70" s="5" t="inlineStr">
         <is>
-          <t>Cataluna tiene articulado con el chocolate dentro: su repertorio de artesania alimentaria incluye «Pasteleria: elaboracion de productos de confiteria, pasteleria, bolleria y reposteria, INCLUIDOS TURRONES Y CHOCOLATES» (`CHN-52`). Es una ACREDITACION VOLUNTARIA y queda PROHIBIDO escribir que sin ella no puedes llamarte artesanal. Y queda PROHIBIDO usar ese decreto como prueba de que es «reposteria» para el RD 1021/2022: es otro registro, otra competencia y otro fin. «Chocolate artesano» no tiene definicion estatal: «artesano», «artesanal» y «casero» tienen CERO ocurrencias en el RD 1055/2003 y en el RD 496/2010 (`CHN-53`). En el resto de comunidades, enlace a su registro.</t>
+          <t>Cataluña tiene articulado con el chocolate dentro: su repertorio de artesanía alimentaria incluye «Pastelería: elaboración de productos de confitería, pastelería, bollería y repostería, INCLUIDOS TURRONES Y CHOCOLATES» (`CHN-52`). Es una ACREDITACION VOLUNTARIA y queda PROHIBIDO escribir que sin ella no puedes llamarte artesanal. Y queda PROHIBIDO usar ese decreto como prueba de que es «repostería» para el RD 1021/2022: es otro registro, otra competencia y otro fin. «Chocolate artesano» no tiene definición estatal: «artesano», «artesanal» y «casero» tienen CERO ocurrencias en el RD 1055/2003 y en el RD 496/2010 (`CHN-53`). En el resto de comunidades, enlace a su registro.</t>
         </is>
       </c>
     </row>
@@ -3767,7 +3767,7 @@
       </c>
       <c r="F74" s="25" t="inlineStr">
         <is>
-          <t>Mi epigrafe es el 644.5, cuya nota permite fabricar bombones «siempre que su comercialización se realice en las propias dependencias de venta». Voy a vender ademas por este canal: Mostrador. Con la Regla 4.a.1 del RDLeg 1175/1990 delante -una cuota faculta exclusivamente para su actividad-, ¿ese canal me obliga a dar otra alta, y cual? Y si la respuesta es el epigrafe industrial 421.1, ¿que consecuencias tiene que el Anexo de la Ley 12/2012 liste el 644.5 y no el 421.1?</t>
+          <t>Mi epígrafe es el 644.5, cuya nota permite fabricar bombones «siempre que su comercialización se realice en las propias dependencias de venta». Voy a vender además por este canal: Mostrador. Con la Regla 4.a.1 del RDLeg 1175/1990 delante -una cuota faculta exclusivamente para su actividad-, ¿ese canal me obliga a dar otra alta, y cual? Y si la respuesta es el epígrafe industrial 421.1, ¿que consecuencias tiene que el Anexo de la Ley 12/2012 liste el 644.5 y no el 421.1?</t>
         </is>
       </c>
       <c r="K74" s="5" t="inlineStr">
@@ -3782,7 +3782,7 @@
       </c>
       <c r="B75" s="9" t="inlineStr">
         <is>
-          <t>Online con envio refrigerado</t>
+          <t>Online con envío refrigerado</t>
         </is>
       </c>
       <c r="C75" s="11" t="inlineStr">
@@ -3802,7 +3802,7 @@
       </c>
       <c r="F75" s="25" t="inlineStr">
         <is>
-          <t>Mi epigrafe es el 644.5, cuya nota permite fabricar bombones «siempre que su comercialización se realice en las propias dependencias de venta». Voy a vender ademas por este canal: Online con envio refrigerado. Con la Regla 4.a.1 del RDLeg 1175/1990 delante -una cuota faculta exclusivamente para su actividad-, ¿ese canal me obliga a dar otra alta, y cual? Y si la respuesta es el epigrafe industrial 421.1, ¿que consecuencias tiene que el Anexo de la Ley 12/2012 liste el 644.5 y no el 421.1?</t>
+          <t>Mi epígrafe es el 644.5, cuya nota permite fabricar bombones «siempre que su comercialización se realice en las propias dependencias de venta». Voy a vender además por este canal: Online con envío refrigerado. Con la Regla 4.a.1 del RDLeg 1175/1990 delante -una cuota faculta exclusivamente para su actividad-, ¿ese canal me obliga a dar otra alta, y cual? Y si la respuesta es el epígrafe industrial 421.1, ¿que consecuencias tiene que el Anexo de la Ley 12/2012 liste el 644.5 y no el 421.1?</t>
         </is>
       </c>
       <c r="K75" s="5" t="inlineStr">
@@ -3817,7 +3817,7 @@
       </c>
       <c r="B76" s="9" t="inlineStr">
         <is>
-          <t>B2B a hosteleria</t>
+          <t>B2B a hostelería</t>
         </is>
       </c>
       <c r="C76" s="11" t="inlineStr">
@@ -3837,7 +3837,7 @@
       </c>
       <c r="F76" s="25" t="inlineStr">
         <is>
-          <t>Mi epigrafe es el 644.5, cuya nota permite fabricar bombones «siempre que su comercialización se realice en las propias dependencias de venta». Voy a vender ademas por este canal: B2B a hosteleria. Con la Regla 4.a.1 del RDLeg 1175/1990 delante -una cuota faculta exclusivamente para su actividad-, ¿ese canal me obliga a dar otra alta, y cual? Y si la respuesta es el epigrafe industrial 421.1, ¿que consecuencias tiene que el Anexo de la Ley 12/2012 liste el 644.5 y no el 421.1?</t>
+          <t>Mi epígrafe es el 644.5, cuya nota permite fabricar bombones «siempre que su comercialización se realice en las propias dependencias de venta». Voy a vender además por este canal: B2B a hostelería. Con la Regla 4.a.1 del RDLeg 1175/1990 delante -una cuota faculta exclusivamente para su actividad-, ¿ese canal me obliga a dar otra alta, y cual? Y si la respuesta es el epígrafe industrial 421.1, ¿que consecuencias tiene que el Anexo de la Ley 12/2012 liste el 644.5 y no el 421.1?</t>
         </is>
       </c>
       <c r="K76" s="5" t="inlineStr">
@@ -3872,7 +3872,7 @@
       </c>
       <c r="F77" s="25" t="inlineStr">
         <is>
-          <t>Mi epigrafe es el 644.5, cuya nota permite fabricar bombones «siempre que su comercialización se realice en las propias dependencias de venta». Voy a vender ademas por este canal: Regalo corporativo. Con la Regla 4.a.1 del RDLeg 1175/1990 delante -una cuota faculta exclusivamente para su actividad-, ¿ese canal me obliga a dar otra alta, y cual? Y si la respuesta es el epigrafe industrial 421.1, ¿que consecuencias tiene que el Anexo de la Ley 12/2012 liste el 644.5 y no el 421.1?</t>
+          <t>Mi epígrafe es el 644.5, cuya nota permite fabricar bombones «siempre que su comercialización se realice en las propias dependencias de venta». Voy a vender además por este canal: Regalo corporativo. Con la Regla 4.a.1 del RDLeg 1175/1990 delante -una cuota faculta exclusivamente para su actividad-, ¿ese canal me obliga a dar otra alta, y cual? Y si la respuesta es el epígrafe industrial 421.1, ¿que consecuencias tiene que el Anexo de la Ley 12/2012 liste el 644.5 y no el 421.1?</t>
         </is>
       </c>
       <c r="K77" s="5" t="inlineStr">
@@ -3907,7 +3907,7 @@
       </c>
       <c r="F78" s="25" t="inlineStr">
         <is>
-          <t>Mi epigrafe es el 644.5, cuya nota permite fabricar bombones «siempre que su comercialización se realice en las propias dependencias de venta». Voy a vender ademas por este canal: Talleres y catas. Con la Regla 4.a.1 del RDLeg 1175/1990 delante -una cuota faculta exclusivamente para su actividad-, ¿ese canal me obliga a dar otra alta, y cual? Y si la respuesta es el epigrafe industrial 421.1, ¿que consecuencias tiene que el Anexo de la Ley 12/2012 liste el 644.5 y no el 421.1?</t>
+          <t>Mi epígrafe es el 644.5, cuya nota permite fabricar bombones «siempre que su comercialización se realice en las propias dependencias de venta». Voy a vender además por este canal: Talleres y catas. Con la Regla 4.a.1 del RDLeg 1175/1990 delante -una cuota faculta exclusivamente para su actividad-, ¿ese canal me obliga a dar otra alta, y cual? Y si la respuesta es el epígrafe industrial 421.1, ¿que consecuencias tiene que el Anexo de la Ley 12/2012 liste el 644.5 y no el 421.1?</t>
         </is>
       </c>
       <c r="K78" s="5" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="B11" s="38" t="inlineStr">
         <is>
-          <t>No lo sé</t>
+          <t>No</t>
         </is>
       </c>
       <c r="C11" s="9" t="inlineStr">
         <is>
-          <t>Depende de si encaja en «cacao en polvo» o es una preparación con otros ingredientes. Míralo referencia a referencia con la denominación legal que le hayas dado en el libro 4.</t>
+          <t>Los puntos 8 y 9 de la Directiva -el chocolate a la taza- quedan FUERA de la nota (14): alimento compuesto, art. 3 del Rgto. 2023/915. Distinto es el cacao en polvo vendido como tal, que sí tiene límite propio: míralo referencia a referencia con la denominación legal que le hayas dado en el libro 4.</t>
         </is>
       </c>
     </row>
@@ -6450,7 +6450,7 @@
       </c>
       <c r="C25" s="9" t="inlineStr">
         <is>
-          <t>Hace la PRIMERA comercializacion en el mercado de la Union, o exporta. Si es tu caso -por ejemplo, importas grano para bean-to-bar-, te toca diligencia debida COMPLETA antes de introducir en el mercado, declaracion presentada previamente, asuncion de responsabilidad y registro de las declaraciones durante cinco anos (`CHN-25`). A ESTE proveedor SI hay que pedirle el numero de referencia de su DDS.</t>
+          <t>Hace la PRIMERA comercialización en el mercado de la Unión, o exporta. Si es tu caso -por ejemplo, importas grano para bean-to-bar-, te toca diligencia debida COMPLETA antes de introducir en el mercado, declaración presentada previamente, asunción de responsabilidad y registro de las declaraciones durante cinco años (`CHN-25`). A ESTE proveedor SI hay que pedirle el número de referencia de su DDS.</t>
         </is>
       </c>
     </row>
@@ -6467,7 +6467,7 @@
       </c>
       <c r="C26" s="9" t="inlineStr">
         <is>
-          <t>Introduce en el mercado productos elaborados con otros productos YA amparados por una declaracion de diligencia debida (`CHN-23`, art. 2.15 ter). Es lo que normalmente sera una chocolateria que compra cobertura ya comercializada en la UE. A este NO se le pide el numero de DDS por el art. 5.3.a).</t>
+          <t>Introduce en el mercado productos elaborados con otros productos YA amparados por una declaración de diligencia debida (`CHN-23`, art. 2.15 ter). Es lo que normalmente será una chocolatería que compra cobertura ya comercializada en la UE. A este NO se le pide el número de DDS por el art. 5.3.a).</t>
         </is>
       </c>
     </row>
@@ -6484,7 +6484,7 @@
       </c>
       <c r="C27" s="9" t="inlineStr">
         <is>
-          <t>Ni introduce ni exporta: comercia dentro. Tampoco se le pide el numero de DDS.</t>
+          <t>Ni introduce ni exporta: comercia dentro. Tampoco se le pide el número de DDS.</t>
         </is>
       </c>
     </row>
@@ -6492,7 +6492,7 @@
     <row r="29" ht="92" customHeight="1">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>REDACCION OBLIGATORIA, y el paso es INFERENCIA DECLARADA, no nivel A: «si tu cobertura llega ya comercializada en la UE y amparada por una declaracion de diligencia debida, eres operador posterior (art. 2.15 ter) y el aplazamiento del art. 38.3 -que es para operadores- no te alcanza: tu fecha es el 30 de diciembre de 2026. Si tu cobertura NO esta amparada (compra anterior al EUDR, proveedor que no lo acredita), la calificacion deja de ser automatica y hay que revisarla». Estan PROHIBIDAS «siempre eres operador posterior» y «tu fecha es el 30-12-2026 pase lo que pase». Y la exclusion de los operadores posteriores del punto 15 se PARAFRASEA, no se entrecomilla: consta en la nota de `CHN-22`, no entre las 81 citas del gate de literalidad. Verificado a 12-09-2026: comprueba el estado del EUDR antes de comprar cacao.</t>
+          <t>REDACCION OBLIGATORIA, y el paso es INFERENCIA DECLARADA, no nivel A: «si tu cobertura llega ya comercializada en la UE y amparada por una declaración de diligencia debida, eres operador posterior (art. 2.15 ter) y el aplazamiento del art. 38.3 -que es para operadores- no te alcanza: tu fecha es el 30 de diciembre de 2026. Si tu cobertura NO esta amparada (compra anterior al EUDR, proveedor que no lo acredita), la calificación deja de ser automática y hay que revisarla». Están PROHIBIDAS «siempre eres operador posterior» y «tu fecha es el 30-12-2026 pase lo que pase». Y la exclusión de los operadores posteriores del punto 15 se PARAFRASEA, no se entrecomilla: consta en la nota de `CHN-22`, no entre las 81 citas del gate de literalidad. Verificado a 12-09-2026: comprueba el estado del EUDR antes de comprar cacao.</t>
         </is>
       </c>
     </row>
@@ -6730,7 +6730,7 @@
       </c>
       <c r="E7" s="43" t="inlineStr">
         <is>
-          <t>Higiene, alérgenos y trazabilidad aplicados a el obrador</t>
+          <t>Higiene, alérgenos y trazabilidad aplicados al obrador</t>
         </is>
       </c>
       <c r="F7" s="14" t="n">
@@ -6762,12 +6762,12 @@
       </c>
       <c r="D8" s="9" t="inlineStr">
         <is>
-          <t>Manana (07:00-15:00)</t>
+          <t>Mañana (07:00-15:00)</t>
         </is>
       </c>
       <c r="E8" s="43" t="inlineStr">
         <is>
-          <t>Higiene, alérgenos y trazabilidad aplicados a el obrador</t>
+          <t>Higiene, alérgenos y trazabilidad aplicados al obrador</t>
         </is>
       </c>
       <c r="F8" s="14" t="n">
@@ -7381,7 +7381,7 @@
       </c>
       <c r="B11" s="9" t="inlineStr">
         <is>
-          <t>Proyecto tecnico visado</t>
+          <t>Proyecto técnico visado</t>
         </is>
       </c>
       <c r="C11" s="37" t="n">
@@ -7431,7 +7431,7 @@
       </c>
       <c r="B12" s="9" t="inlineStr">
         <is>
-          <t>Declaracion responsable de actividad (no licencia previa)</t>
+          <t>Declaración responsable de actividad (no licencia previa)</t>
         </is>
       </c>
       <c r="C12" s="37" t="n">
@@ -7486,7 +7486,7 @@
       </c>
       <c r="B13" s="9" t="inlineStr">
         <is>
-          <t>Obra y adecuacion del local</t>
+          <t>Obra y adecuación del local</t>
         </is>
       </c>
       <c r="C13" s="37" t="n">
@@ -7591,7 +7591,7 @@
       </c>
       <c r="B15" s="9" t="inlineStr">
         <is>
-          <t>Climatizacion y deshumidificacion</t>
+          <t>Climatización y deshumidificación</t>
         </is>
       </c>
       <c r="C15" s="37" t="n">
@@ -7696,7 +7696,7 @@
       </c>
       <c r="B17" s="9" t="inlineStr">
         <is>
-          <t>Comunicacion al registro sanitario autonomico</t>
+          <t>Comunicación al registro sanitario autonómico</t>
         </is>
       </c>
       <c r="C17" s="37" t="n">
@@ -7751,7 +7751,7 @@
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
-          <t>Plan de APPCC, alergenos y registro de formacion</t>
+          <t>Plan de APPCC, alérgenos y registro de formación</t>
         </is>
       </c>
       <c r="C18" s="37" t="n">
@@ -7801,7 +7801,7 @@
       </c>
       <c r="B19" s="9" t="inlineStr">
         <is>
-          <t>Contratacion del equipo y altas en Seguridad Social</t>
+          <t>Contratación del equipo y altas en Seguridad Social</t>
         </is>
       </c>
       <c r="C19" s="37" t="n">
@@ -9176,7 +9176,7 @@
       </c>
       <c r="B58" s="9" t="inlineStr">
         <is>
-          <t>San Valentin</t>
+          <t>San Valentín</t>
         </is>
       </c>
       <c r="C58" s="12" t="inlineStr">
@@ -9196,7 +9196,7 @@
       </c>
       <c r="B59" s="9" t="inlineStr">
         <is>
-          <t>Dia del Padre</t>
+          <t>Día del Padre</t>
         </is>
       </c>
       <c r="C59" s="12" t="inlineStr">
@@ -9236,7 +9236,7 @@
       </c>
       <c r="B61" s="9" t="inlineStr">
         <is>
-          <t>COMUNIONES (pico) y Dia de la Madre</t>
+          <t>COMUNIONES (pico) y Día de la Madre</t>
         </is>
       </c>
       <c r="C61" s="12" t="inlineStr">
@@ -9256,7 +9256,7 @@
       </c>
       <c r="B62" s="9" t="inlineStr">
         <is>
-          <t>COMUNIONES (ultimas)</t>
+          <t>COMUNIONES (últimas)</t>
         </is>
       </c>
       <c r="C62" s="12" t="inlineStr">

--- a/astro-site/public/dl/guia-chocolateria-obrador/checklist-legal-licencias-y-cacao.xlsx
+++ b/astro-site/public/dl/guia-chocolateria-obrador/checklist-legal-licencias-y-cacao.xlsx
@@ -2381,7 +2381,7 @@
       </c>
       <c r="K27" s="5" t="inlineStr">
         <is>
-          <t>La lista estatal del obrador en vivienda tiene CINCO letras y la quinta es ABIERTA: «otros alimentos que las autoridades competentes de las comunidades autónomas permitan en sus territorios» (`CHN-44`). Por defecto el chocolate no encaja en la letra b), pero eso es INTERPRETACION DECLARADA (`CHN-44-int`), no nivel A: compruebalo en tu comunidad. La letra b) valenciana añade «confitería», NO «chocolate» (`CHN-44b`). PROHIBIDO «hacer bombones en casa para vender es ilegal en Espana». Y el tope de 100 kg/semana del art. 13.9 solo se activa si esta casilla esta en «si»: son TRES requisitos, no uno -volumen PROPORCIONAL AL TAMAÑO DE LAS INSTALACIONES, tope de 100 kg/semana y demostrable documentalmente- y el que de verdad limita es el primero (`PA-29c`, reutilizado de Pastelería y verificado el 10-09-2026).  [Fuente: CHN-44 + CHN-44-int + CHN-44b]</t>
+          <t>La lista estatal del obrador en vivienda tiene CINCO letras y la quinta es ABIERTA: «otros alimentos que las autoridades competentes de las comunidades autónomas permitan en sus territorios» (`CHN-44`). Por defecto el chocolate no encaja en la letra b), pero eso es INTERPRETACION DECLARADA (`CHN-44-int`), no nivel A: compruebalo en tu comunidad. La letra b) valenciana añade «confitería», NO «chocolate» (`CHN-44b`). PROHIBIDO «hacer bombones en casa para vender es ilegal en España». Y el tope de 100 kg/semana del art. 13.9 solo se activa si esta casilla esta en «si»: son TRES requisitos, no uno -volumen PROPORCIONAL AL TAMAÑO DE LAS INSTALACIONES, tope de 100 kg/semana y demostrable documentalmente- y el que de verdad limita es el primero (`PA-29c`, reutilizado de Pastelería y verificado el 10-09-2026).  [Fuente: CHN-44 + CHN-44-int + CHN-44b]</t>
         </is>
       </c>
     </row>
@@ -6450,7 +6450,7 @@
       </c>
       <c r="C25" s="9" t="inlineStr">
         <is>
-          <t>Hace la PRIMERA comercialización en el mercado de la Unión, o exporta. Si es tu caso -por ejemplo, importas grano para bean-to-bar-, te toca diligencia debida COMPLETA antes de introducir en el mercado, declaración presentada previamente, asunción de responsabilidad y registro de las declaraciones durante cinco años (`CHN-25`). A ESTE proveedor SI hay que pedirle el número de referencia de su DDS.</t>
+          <t>Hace la PRIMERA comercialización en el mercado de la Unión, o exporta. Si es tu caso -por ejemplo, importas grano para bean-to-bar-, te toca diligencia debida COMPLETA antes de introducir en el mercado, declaración presentada previamente, asunción de responsabilidad y registro de las declaraciones durante cinco años (CHN-25). A ESTE proveedor SI hay que pedirle el número de referencia de su DDS.</t>
         </is>
       </c>
     </row>
@@ -6467,7 +6467,7 @@
       </c>
       <c r="C26" s="9" t="inlineStr">
         <is>
-          <t>Introduce en el mercado productos elaborados con otros productos YA amparados por una declaración de diligencia debida (`CHN-23`, art. 2.15 ter). Es lo que normalmente será una chocolatería que compra cobertura ya comercializada en la UE. A este NO se le pide el número de DDS por el art. 5.3.a).</t>
+          <t>Introduce en el mercado productos elaborados con otros productos YA amparados por una declaración de diligencia debida (CHN-23, art. 2.15 ter). Es lo que normalmente será una chocolatería que compra cobertura ya comercializada en la UE. A este NO se le pide el número de DDS por el art. 5.3.a).</t>
         </is>
       </c>
     </row>

--- a/astro-site/public/dl/guia-chocolateria-obrador/checklist-legal-licencias-y-cacao.xlsx
+++ b/astro-site/public/dl/guia-chocolateria-obrador/checklist-legal-licencias-y-cacao.xlsx
@@ -6406,7 +6406,7 @@
         </is>
       </c>
       <c r="B21" s="29" t="str">
-        <f>IFERROR(IF(B18="","","El paso «una chocolatería que compra cobertura es operador posterior, así que el aplazamiento del art. 38.3 no le alcanza» es una INFERENCIA nuestra, con el art. 2.15 ter como condición. Si tu cobertura NO está amparada, la calificación deja de ser automática y hay que revisarla"),"")</f>
+        <f>IFERROR(IF(B18="","","El paso «una chocolatería que compra cobertura es operador posterior, así que el aplazamiento del art. 38.3 no le alcanza» es una INFERENCIA nuestra, con el art. 2.15 ter como condición. Si tu cobertura NO está amparada, la calificación "&amp;"deja de ser automática y hay que revisarla"),"")</f>
         <v>El paso «una chocolatería que compra cobertura es operador posterior, así que el aplazamiento del art. 38.3 no le alcanza» es una INFERENCIA nuestra, con el art. 2.15 ter como condición. Si tu cobertura NO está amparada, la calificación deja de ser automática y hay que revisarla</v>
       </c>
     </row>
